--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Coyhaique</t>
   </si>
   <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
-    <t xml:space="preserve">O'Higgins</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:43</t>
+    <t xml:space="preserve">2026-09-09 23:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -638,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11303</v>
+        <v>11302</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -651,7 +651,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11302</v>
+        <v>11303</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:42</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:31</t>
+    <t xml:space="preserve">2026-09-23 13:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -640,7 +640,9 @@
       <c r="C10" s="2" t="n">
         <v>11302</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
@@ -653,7 +655,9 @@
       <c r="C11" s="2" t="n">
         <v>11303</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E11" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:04</t>
+    <t xml:space="preserve">2026-10-02 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:37</t>
+    <t xml:space="preserve">2026-10-04 09:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:49</t>
+    <t xml:space="preserve">2026-10-05 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
